--- a/docs/pin_list.xlsx
+++ b/docs/pin_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/kyoto-ths/02/pinlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{80FD4C0D-4061-4E0A-82DD-26CB8133CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7603E8FB-6F77-4736-9AEF-E0F5014323C6}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{80FD4C0D-4061-4E0A-82DD-26CB8133CE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D5B0801-CC14-4BFE-A561-D1A11C19DAF6}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="220" windowWidth="19200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,8 +82,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>zawa</t>
-    <phoneticPr fontId="1"/>
+    <t>KabechiFC</t>
   </si>
 </sst>
 </file>
@@ -216,6 +215,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
